--- a/data/AP Sales Summary.xlsx
+++ b/data/AP Sales Summary.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -399,10 +399,10 @@
         <v>2020</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>1089</v>
+        <v>840</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -410,10 +410,10 @@
         <v>2020</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>717</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -421,10 +421,10 @@
         <v>2020</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>783</v>
+        <v>717</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -432,10 +432,10 @@
         <v>2020</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>886</v>
+        <v>783</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -443,10 +443,10 @@
         <v>2020</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>974</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -454,10 +454,10 @@
         <v>2020</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>1023</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -465,10 +465,10 @@
         <v>2020</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>994</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -476,10 +476,10 @@
         <v>2020</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1270</v>
+        <v>994</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -487,10 +487,10 @@
         <v>2020</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>801</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -498,10 +498,10 @@
         <v>2020</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>702</v>
+        <v>801</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -509,21 +509,21 @@
         <v>2020</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>614</v>
+        <v>702</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>750</v>
+        <v>614</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -531,10 +531,10 @@
         <v>2021</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>1043</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -542,10 +542,10 @@
         <v>2021</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>1070</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -553,10 +553,10 @@
         <v>2021</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>1113</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -564,10 +564,10 @@
         <v>2021</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>939</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -575,10 +575,10 @@
         <v>2021</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>1059</v>
+        <v>939</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -586,10 +586,10 @@
         <v>2021</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>1072</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -597,10 +597,10 @@
         <v>2021</v>
       </c>
       <c r="B20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>1121</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -608,10 +608,10 @@
         <v>2021</v>
       </c>
       <c r="B21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
-        <v>993</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -619,10 +619,10 @@
         <v>2021</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>1002</v>
+        <v>993</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -630,10 +630,10 @@
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>866</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -641,21 +641,21 @@
         <v>2021</v>
       </c>
       <c r="B24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
-        <v>1018</v>
+        <v>866</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>995</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -663,10 +663,10 @@
         <v>2022</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>1078</v>
+        <v>995</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -674,10 +674,10 @@
         <v>2022</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>1115</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -685,10 +685,10 @@
         <v>2022</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>1048</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -696,10 +696,10 @@
         <v>2022</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>903</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -707,10 +707,10 @@
         <v>2022</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>963</v>
+        <v>903</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -718,10 +718,10 @@
         <v>2022</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>1109</v>
+        <v>963</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -729,10 +729,10 @@
         <v>2022</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>1147</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -740,10 +740,10 @@
         <v>2022</v>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>1317</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -751,10 +751,10 @@
         <v>2022</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34">
-        <v>1234</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -762,10 +762,10 @@
         <v>2022</v>
       </c>
       <c r="B35">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>958</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -773,21 +773,21 @@
         <v>2022</v>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36">
-        <v>782</v>
+        <v>958</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C37">
-        <v>602</v>
+        <v>782</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -795,10 +795,10 @@
         <v>2023</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>862</v>
+        <v>602</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -806,10 +806,10 @@
         <v>2023</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>1114</v>
+        <v>862</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -817,10 +817,10 @@
         <v>2023</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>1089</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -828,10 +828,10 @@
         <v>2023</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>1149</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -839,10 +839,10 @@
         <v>2023</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42">
-        <v>1628</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -850,10 +850,10 @@
         <v>2023</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43">
-        <v>1564</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -861,10 +861,10 @@
         <v>2023</v>
       </c>
       <c r="B44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>1166</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -872,10 +872,10 @@
         <v>2023</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45">
-        <v>1269</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -883,10 +883,10 @@
         <v>2023</v>
       </c>
       <c r="B46">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46">
-        <v>1394</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -894,10 +894,10 @@
         <v>2023</v>
       </c>
       <c r="B47">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C47">
-        <v>1377</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -905,21 +905,21 @@
         <v>2023</v>
       </c>
       <c r="B48">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C48">
-        <v>1095</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C49">
-        <v>1210</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -927,10 +927,10 @@
         <v>2024</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>1512</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -938,10 +938,10 @@
         <v>2024</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>1558</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -949,10 +949,10 @@
         <v>2024</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>1598</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -960,10 +960,10 @@
         <v>2024</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>1683</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -971,10 +971,10 @@
         <v>2024</v>
       </c>
       <c r="B54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>1589</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -982,10 +982,10 @@
         <v>2024</v>
       </c>
       <c r="B55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55">
-        <v>1829</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -993,10 +993,10 @@
         <v>2024</v>
       </c>
       <c r="B56">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C56">
-        <v>1702</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1004,10 +1004,10 @@
         <v>2024</v>
       </c>
       <c r="B57">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C57">
-        <v>1473</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1015,10 +1015,10 @@
         <v>2024</v>
       </c>
       <c r="B58">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C58">
-        <v>1626</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1026,10 +1026,10 @@
         <v>2024</v>
       </c>
       <c r="B59">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59">
-        <v>1406</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1037,21 +1037,21 @@
         <v>2024</v>
       </c>
       <c r="B60">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60">
-        <v>1456</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C61">
-        <v>1673</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1059,10 +1059,10 @@
         <v>2025</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>2030</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1070,10 +1070,10 @@
         <v>2025</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>2276</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1081,10 +1081,10 @@
         <v>2025</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>2281</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1092,10 +1092,10 @@
         <v>2025</v>
       </c>
       <c r="B65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65">
-        <v>2134</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1103,10 +1103,10 @@
         <v>2025</v>
       </c>
       <c r="B66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66">
-        <v>2175</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1114,10 +1114,10 @@
         <v>2025</v>
       </c>
       <c r="B67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C67">
-        <v>2172</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1125,10 +1125,10 @@
         <v>2025</v>
       </c>
       <c r="B68">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68">
-        <v>1902</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1136,10 +1136,10 @@
         <v>2025</v>
       </c>
       <c r="B69">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C69">
-        <v>2008</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1147,10 +1147,10 @@
         <v>2025</v>
       </c>
       <c r="B70">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C70">
-        <v>1691</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1158,10 +1158,10 @@
         <v>2025</v>
       </c>
       <c r="B71">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71">
-        <v>1759</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1169,21 +1169,21 @@
         <v>2025</v>
       </c>
       <c r="B72">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C72">
-        <v>1720</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C73">
-        <v>1894</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1191,10 +1191,10 @@
         <v>2026</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>1650</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1202,42 +1202,9 @@
         <v>2026</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>1894</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76">
-        <v>2026</v>
-      </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77">
-        <v>2026</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77">
-        <v>1894</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78">
-        <v>2026</v>
-      </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="C78">
         <v>1650</v>
       </c>
     </row>

--- a/data/AP Sales Summary.xlsx
+++ b/data/AP Sales Summary.xlsx
@@ -1205,7 +1205,7 @@
         <v>2</v>
       </c>
       <c r="C75">
-        <v>1650</v>
+        <v>1656</v>
       </c>
     </row>
   </sheetData>

--- a/data/AP Sales Summary.xlsx
+++ b/data/AP Sales Summary.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1208,6 +1208,17 @@
         <v>1656</v>
       </c>
     </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>2026</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
+      </c>
+      <c r="C76">
+        <v>1834</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AP Sales Summary.xlsx
+++ b/data/AP Sales Summary.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1216,7 +1216,18 @@
         <v>3</v>
       </c>
       <c r="C76">
-        <v>1834</v>
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>2026</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77">
+        <v>1705</v>
       </c>
     </row>
   </sheetData>

--- a/data/AP Sales Summary.xlsx
+++ b/data/AP Sales Summary.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1230,6 +1230,17 @@
         <v>1705</v>
       </c>
     </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
+        <v>2026</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+      <c r="C78">
+        <v>1629</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AP Sales Summary.xlsx
+++ b/data/AP Sales Summary.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1241,6 +1241,17 @@
         <v>1629</v>
       </c>
     </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>2026</v>
+      </c>
+      <c r="B79">
+        <v>6</v>
+      </c>
+      <c r="C79">
+        <v>1824</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
